--- a/docentes/González Nuñez Veronica - Estadisticos 20212.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="109">
   <si>
     <t>Mat</t>
   </si>
@@ -83,6 +83,267 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MELENDEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>PEÑA</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LIMON</t>
+  </si>
+  <si>
+    <t>MARCIAL</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>DE LA ROSA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
+    <t>ESPERON</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>SILVERIO</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>ALEXIS ISAI</t>
+  </si>
+  <si>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>ANALI</t>
+  </si>
+  <si>
+    <t>DULCE FERNANDA</t>
+  </si>
+  <si>
+    <t>FRIDA SOFIA</t>
+  </si>
+  <si>
+    <t>ANTONIO ABIDAN</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>MILAGROS</t>
+  </si>
+  <si>
+    <t>MARITZA JULIANA</t>
+  </si>
+  <si>
+    <t>LESLIE</t>
+  </si>
+  <si>
+    <t>HEIDY MARIAM</t>
+  </si>
+  <si>
+    <t>YEILI DAYNERIS</t>
+  </si>
+  <si>
+    <t>JULIO CESAR</t>
+  </si>
+  <si>
+    <t>INGRID SARAI</t>
+  </si>
+  <si>
+    <t>SUSANA</t>
+  </si>
+  <si>
+    <t>JOSSELIN ANDREA</t>
+  </si>
+  <si>
+    <t>LUIS DIEGO</t>
+  </si>
+  <si>
+    <t>MELANIE NAOMI</t>
+  </si>
+  <si>
+    <t>AMARANTA DENISSE</t>
+  </si>
+  <si>
+    <t>KIMBERLY ALONDRA</t>
+  </si>
+  <si>
+    <t>MARIJOSE</t>
+  </si>
+  <si>
+    <t>IVAN DE JESUS</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>INGRID YALITH</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>ALONDRA</t>
+  </si>
+  <si>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>ROGELIO</t>
+  </si>
+  <si>
+    <t>MICHELLE ROBERTA</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>MIA VALENTINA</t>
+  </si>
+  <si>
+    <t>EMILY</t>
   </si>
 </sst>
 </file>
@@ -532,19 +793,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>7.14</v>
+        <v>10.71</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -721,7 +982,7 @@
         <v>28</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -898,19 +1159,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>7.14</v>
+        <v>10.71</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -995,7 +1256,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1025,6 +1286,785 @@
         <v>21</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920145</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920190</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920191</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920193</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920199</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920200</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920201</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>19330051920280</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920206</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920208</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>19330051920290</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>20330051920209</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920210</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920212</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920213</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" t="s">
+        <v>89</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>19330051920177</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>20330051920217</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" t="s">
+        <v>91</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920115</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>20330051920116</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" t="s">
+        <v>93</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>20330051920128</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20330051920131</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" t="s">
+        <v>95</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920136</v>
+      </c>
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" t="s">
+        <v>96</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>20330051920140</v>
+      </c>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>20330051920141</v>
+      </c>
+      <c r="B25" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>20330051920142</v>
+      </c>
+      <c r="B26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" t="s">
+        <v>99</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>20330051920143</v>
+      </c>
+      <c r="B27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>20330051920144</v>
+      </c>
+      <c r="B28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" t="s">
+        <v>101</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>20330051920153</v>
+      </c>
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" t="s">
+        <v>102</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>20330051920317</v>
+      </c>
+      <c r="B30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" t="s">
+        <v>103</v>
+      </c>
+      <c r="E30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>20330051920380</v>
+      </c>
+      <c r="B31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" t="s">
+        <v>71</v>
+      </c>
+      <c r="D31" t="s">
+        <v>104</v>
+      </c>
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>20330051920331</v>
+      </c>
+      <c r="B32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" t="s">
+        <v>105</v>
+      </c>
+      <c r="E32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>20330051920192</v>
+      </c>
+      <c r="B33" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33" t="s">
+        <v>106</v>
+      </c>
+      <c r="E33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>20330051920197</v>
+      </c>
+      <c r="B34" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" t="s">
+        <v>107</v>
+      </c>
+      <c r="E34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>20330051920219</v>
+      </c>
+      <c r="B35" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" t="s">
+        <v>108</v>
+      </c>
+      <c r="E35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/González Nuñez Veronica - Estadisticos 20212.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="125">
   <si>
     <t>Mat</t>
   </si>
@@ -88,181 +88,205 @@
     <t>ORTEGA</t>
   </si>
   <si>
-    <t>ASCENCION</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MELENDEZ</t>
+  </si>
+  <si>
+    <t>PEÑA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MAYA</t>
+  </si>
+  <si>
+    <t>OCAÑA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ESPERON</t>
   </si>
   <si>
     <t>CARRERA</t>
   </si>
   <si>
+    <t>LIMON</t>
+  </si>
+  <si>
+    <t>MARCIAL</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>DE LA ROSA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MELENDEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LIMON</t>
-  </si>
-  <si>
-    <t>MARCIAL</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>DE LA ROSA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>ESPERON</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
+    <t>APARICIO</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>TZIZIHUA</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>SILVERIO</t>
   </si>
   <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>SILVERIO</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
     <t>ALEXIS ISAI</t>
   </si>
   <si>
-    <t>REYNA ARISBETH</t>
-  </si>
-  <si>
-    <t>ANALI</t>
-  </si>
-  <si>
-    <t>DULCE FERNANDA</t>
-  </si>
-  <si>
-    <t>FRIDA SOFIA</t>
-  </si>
-  <si>
-    <t>ANTONIO ABIDAN</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>ALDIR ADALBERTO</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
   </si>
   <si>
     <t>MILAGROS</t>
@@ -271,21 +295,9 @@
     <t>MARITZA JULIANA</t>
   </si>
   <si>
-    <t>LESLIE</t>
-  </si>
-  <si>
-    <t>HEIDY MARIAM</t>
-  </si>
-  <si>
     <t>YEILI DAYNERIS</t>
   </si>
   <si>
-    <t>JULIO CESAR</t>
-  </si>
-  <si>
-    <t>INGRID SARAI</t>
-  </si>
-  <si>
     <t>SUSANA</t>
   </si>
   <si>
@@ -295,9 +307,57 @@
     <t>LUIS DIEGO</t>
   </si>
   <si>
+    <t>AXEL YAEL</t>
+  </si>
+  <si>
     <t>MELANIE NAOMI</t>
   </si>
   <si>
+    <t>YAZMIN</t>
+  </si>
+  <si>
+    <t>GERMAN ERNESTO</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>XIMENA MICHELL</t>
+  </si>
+  <si>
+    <t>GUILLERMO SAID</t>
+  </si>
+  <si>
+    <t>SURISADAY</t>
+  </si>
+  <si>
+    <t>JESUS SAMUEL</t>
+  </si>
+  <si>
+    <t>ARIZBETH</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>FRANCISCO YAEL</t>
+  </si>
+  <si>
+    <t>OZIEL</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>DORA LUZ</t>
+  </si>
+  <si>
+    <t>MIA VALENTINA</t>
+  </si>
+  <si>
     <t>AMARANTA DENISSE</t>
   </si>
   <si>
@@ -313,9 +373,6 @@
     <t>MARIA FERNANDA</t>
   </si>
   <si>
-    <t>KARLA</t>
-  </si>
-  <si>
     <t>INGRID YALITH</t>
   </si>
   <si>
@@ -335,15 +392,6 @@
   </si>
   <si>
     <t>MICHELLE ROBERTA</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>MIA VALENTINA</t>
-  </si>
-  <si>
-    <t>EMILY</t>
   </si>
 </sst>
 </file>
@@ -770,16 +818,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="H3">
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -793,16 +844,16 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>10.71</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="H4">
         <v>8</v>
@@ -819,16 +870,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>63.16</v>
+      </c>
+      <c r="H5">
+        <v>7.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -959,7 +1013,7 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -982,7 +1036,7 @@
         <v>28</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1005,7 +1059,7 @@
         <v>19</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1136,16 +1190,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="H3">
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1159,16 +1216,16 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>10.71</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="H4">
         <v>8</v>
@@ -1185,16 +1242,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>63.16</v>
+      </c>
+      <c r="H5">
+        <v>7.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1256,7 +1316,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1294,10 +1354,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1311,22 +1371,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920190</v>
+        <v>20330051920087</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1334,22 +1394,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920191</v>
+        <v>20330051920091</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1357,22 +1417,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920193</v>
+        <v>20330051920065</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1380,22 +1440,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920199</v>
+        <v>20330051920068</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1403,16 +1463,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920200</v>
+        <v>19330051920280</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1426,16 +1486,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920201</v>
+        <v>20330051920206</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1449,16 +1509,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920280</v>
+        <v>20330051920209</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1472,16 +1532,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920206</v>
+        <v>20330051920213</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1495,16 +1555,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920208</v>
+        <v>19330051920177</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1518,16 +1578,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920290</v>
+        <v>20330051920217</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1541,22 +1601,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920209</v>
+        <v>20330051920279</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1564,22 +1624,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920210</v>
+        <v>20330051920115</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1587,22 +1647,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920212</v>
+        <v>20330051920129</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1610,22 +1670,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920213</v>
+        <v>20330051920134</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D16" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1633,22 +1693,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920177</v>
+        <v>20330051920141</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1656,22 +1716,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920217</v>
+        <v>20330051920145</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1679,22 +1739,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920115</v>
+        <v>20330051920318</v>
       </c>
       <c r="B19" t="s">
         <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -1702,22 +1762,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920116</v>
+        <v>20330051920321</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1725,22 +1785,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920128</v>
+        <v>20330051920323</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D21" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1748,22 +1808,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920131</v>
+        <v>20330051920324</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -1771,22 +1831,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920136</v>
+        <v>20330051920325</v>
       </c>
       <c r="B23" t="s">
         <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D23" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -1794,22 +1854,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920140</v>
+        <v>20330051920326</v>
       </c>
       <c r="B24" t="s">
         <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -1817,22 +1877,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920141</v>
+        <v>20330051920327</v>
       </c>
       <c r="B25" t="s">
         <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="D25" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -1840,22 +1900,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920142</v>
+        <v>20330051920330</v>
       </c>
       <c r="B26" t="s">
         <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="D26" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1863,22 +1923,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920143</v>
+        <v>20330051920333</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D27" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1886,22 +1946,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920144</v>
+        <v>20330051920335</v>
       </c>
       <c r="B28" t="s">
         <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D28" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1909,111 +1969,114 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>20330051920153</v>
+        <v>20330051920197</v>
       </c>
       <c r="B29" t="s">
         <v>46</v>
       </c>
+      <c r="C29" t="s">
+        <v>76</v>
+      </c>
       <c r="D29" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>20330051920317</v>
+        <v>20330051920116</v>
       </c>
       <c r="B30" t="s">
         <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D30" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>20330051920380</v>
+        <v>20330051920128</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D31" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>20330051920331</v>
+        <v>20330051920131</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C32" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="D32" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>20330051920192</v>
+        <v>20330051920136</v>
       </c>
       <c r="B33" t="s">
         <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D33" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2021,22 +2084,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>20330051920197</v>
+        <v>20330051920140</v>
       </c>
       <c r="B34" t="s">
         <v>50</v>
       </c>
       <c r="C34" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D34" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -2044,24 +2107,159 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>20330051920219</v>
+        <v>20330051920142</v>
       </c>
       <c r="B35" t="s">
         <v>51</v>
       </c>
       <c r="C35" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="D35" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
       </c>
       <c r="F35" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>20330051920143</v>
+      </c>
+      <c r="B36" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" t="s">
+        <v>81</v>
+      </c>
+      <c r="D36" t="s">
+        <v>119</v>
+      </c>
+      <c r="E36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>20330051920144</v>
+      </c>
+      <c r="B37" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" t="s">
+        <v>120</v>
+      </c>
+      <c r="E37" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>20330051920153</v>
+      </c>
+      <c r="B38" t="s">
+        <v>54</v>
+      </c>
+      <c r="D38" t="s">
+        <v>121</v>
+      </c>
+      <c r="E38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>20330051920317</v>
+      </c>
+      <c r="B39" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39" t="s">
+        <v>122</v>
+      </c>
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>20330051920380</v>
+      </c>
+      <c r="B40" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" t="s">
+        <v>123</v>
+      </c>
+      <c r="E40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>20330051920331</v>
+      </c>
+      <c r="B41" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" t="s">
+        <v>124</v>
+      </c>
+      <c r="E41" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20212.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="122">
   <si>
     <t>Mat</t>
   </si>
@@ -136,9 +136,6 @@
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -229,9 +226,6 @@
     <t>HUERTA</t>
   </si>
   <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
     <t>LEON</t>
   </si>
   <si>
@@ -326,9 +320,6 @@
   </si>
   <si>
     <t>GUILLERMO SAID</t>
-  </si>
-  <si>
-    <t>SURISADAY</t>
   </si>
   <si>
     <t>JESUS SAMUEL</t>
@@ -922,19 +913,19 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>5.26</v>
+        <v>15.79</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -1105,7 +1096,7 @@
         <v>19</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1294,19 +1285,19 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>5.26</v>
+        <v>15.79</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -1316,7 +1307,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1354,10 +1345,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1377,10 +1368,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1400,10 +1391,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1423,10 +1414,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1449,7 +1440,7 @@
         <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1469,10 +1460,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1495,7 +1486,7 @@
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1515,10 +1506,10 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1538,10 +1529,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1564,7 +1555,7 @@
         <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1584,10 +1575,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1607,10 +1598,10 @@
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1630,10 +1621,10 @@
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1653,10 +1644,10 @@
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1676,10 +1667,10 @@
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -1699,10 +1690,10 @@
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -1722,10 +1713,10 @@
         <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -1745,10 +1736,10 @@
         <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -1762,16 +1753,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920321</v>
+        <v>20330051920323</v>
       </c>
       <c r="B20" t="s">
         <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D20" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -1785,16 +1776,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920323</v>
+        <v>20330051920324</v>
       </c>
       <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
         <v>40</v>
       </c>
-      <c r="C21" t="s">
-        <v>71</v>
-      </c>
       <c r="D21" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -1808,16 +1799,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920324</v>
+        <v>20330051920325</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -1831,16 +1822,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920325</v>
+        <v>20330051920326</v>
       </c>
       <c r="B23" t="s">
         <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -1854,16 +1845,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920326</v>
+        <v>20330051920327</v>
       </c>
       <c r="B24" t="s">
         <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="D24" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
@@ -1877,16 +1868,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920327</v>
+        <v>20330051920330</v>
       </c>
       <c r="B25" t="s">
         <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="D25" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
@@ -1900,16 +1891,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920330</v>
+        <v>20330051920333</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D26" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
@@ -1923,16 +1914,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920333</v>
+        <v>20330051920335</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
@@ -1946,45 +1937,45 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920335</v>
+        <v>20330051920197</v>
       </c>
       <c r="B28" t="s">
         <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>20330051920197</v>
+        <v>20330051920116</v>
       </c>
       <c r="B29" t="s">
         <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -1992,16 +1983,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>20330051920116</v>
+        <v>20330051920128</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D30" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E30" t="s">
         <v>9</v>
@@ -2015,16 +2006,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>20330051920128</v>
+        <v>20330051920131</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D31" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
@@ -2038,16 +2029,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>20330051920131</v>
+        <v>20330051920136</v>
       </c>
       <c r="B32" t="s">
         <v>48</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D32" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
@@ -2061,16 +2052,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>20330051920136</v>
+        <v>20330051920140</v>
       </c>
       <c r="B33" t="s">
         <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D33" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
@@ -2084,16 +2075,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>20330051920140</v>
+        <v>20330051920142</v>
       </c>
       <c r="B34" t="s">
         <v>50</v>
       </c>
       <c r="C34" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="D34" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
@@ -2107,16 +2098,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>20330051920142</v>
+        <v>20330051920143</v>
       </c>
       <c r="B35" t="s">
         <v>51</v>
       </c>
       <c r="C35" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
@@ -2130,16 +2121,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>20330051920143</v>
+        <v>20330051920144</v>
       </c>
       <c r="B36" t="s">
         <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="D36" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E36" t="s">
         <v>9</v>
@@ -2153,16 +2144,13 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>20330051920144</v>
+        <v>20330051920153</v>
       </c>
       <c r="B37" t="s">
         <v>53</v>
       </c>
-      <c r="C37" t="s">
-        <v>57</v>
-      </c>
       <c r="D37" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E37" t="s">
         <v>9</v>
@@ -2176,19 +2164,22 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>20330051920153</v>
+        <v>20330051920317</v>
       </c>
       <c r="B38" t="s">
         <v>54</v>
       </c>
+      <c r="C38" t="s">
+        <v>80</v>
+      </c>
       <c r="D38" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E38" t="s">
         <v>9</v>
       </c>
       <c r="F38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -2196,16 +2187,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>20330051920317</v>
+        <v>20330051920380</v>
       </c>
       <c r="B39" t="s">
         <v>55</v>
       </c>
       <c r="C39" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D39" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E39" t="s">
         <v>9</v>
@@ -2219,16 +2210,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>20330051920380</v>
+        <v>20330051920331</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C40" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E40" t="s">
         <v>9</v>
@@ -2237,29 +2228,6 @@
         <v>15</v>
       </c>
       <c r="G40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>20330051920331</v>
-      </c>
-      <c r="B41" t="s">
-        <v>30</v>
-      </c>
-      <c r="C41" t="s">
-        <v>84</v>
-      </c>
-      <c r="D41" t="s">
-        <v>124</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
-        <v>15</v>
-      </c>
-      <c r="G41">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20212.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="48">
   <si>
     <t>Mat</t>
   </si>
@@ -100,174 +100,42 @@
     <t>TEXCAHUA</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>MARCIAL</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>MELENDEZ</t>
-  </si>
-  <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MAYA</t>
-  </si>
-  <si>
-    <t>OCAÑA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ESPERON</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>LIMON</t>
-  </si>
-  <si>
-    <t>MARCIAL</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>DE LA ROSA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>APARICIO</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
     <t>MACHORRO</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
-    <t>SILVERIO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>ALEXIS ISAI</t>
   </si>
   <si>
@@ -283,106 +151,16 @@
     <t>JONATHAN</t>
   </si>
   <si>
-    <t>MILAGROS</t>
-  </si>
-  <si>
-    <t>MARITZA JULIANA</t>
-  </si>
-  <si>
-    <t>YEILI DAYNERIS</t>
-  </si>
-  <si>
-    <t>SUSANA</t>
-  </si>
-  <si>
-    <t>JOSSELIN ANDREA</t>
-  </si>
-  <si>
-    <t>LUIS DIEGO</t>
-  </si>
-  <si>
     <t>AXEL YAEL</t>
   </si>
   <si>
-    <t>MELANIE NAOMI</t>
-  </si>
-  <si>
-    <t>YAZMIN</t>
-  </si>
-  <si>
-    <t>GERMAN ERNESTO</t>
-  </si>
-  <si>
     <t>KARLA</t>
   </si>
   <si>
-    <t>XIMENA MICHELL</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAID</t>
-  </si>
-  <si>
-    <t>JESUS SAMUEL</t>
-  </si>
-  <si>
-    <t>ARIZBETH</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
-  </si>
-  <si>
-    <t>FRANCISCO YAEL</t>
-  </si>
-  <si>
-    <t>OZIEL</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>DORA LUZ</t>
-  </si>
-  <si>
-    <t>MIA VALENTINA</t>
-  </si>
-  <si>
-    <t>AMARANTA DENISSE</t>
-  </si>
-  <si>
-    <t>KIMBERLY ALONDRA</t>
-  </si>
-  <si>
-    <t>MARIJOSE</t>
-  </si>
-  <si>
     <t>IVAN DE JESUS</t>
   </si>
   <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>INGRID YALITH</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>ALONDRA</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
-  </si>
-  <si>
     <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>MICHELLE ROBERTA</t>
   </si>
 </sst>
 </file>
@@ -835,19 +613,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>64.29000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -887,19 +665,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="G6">
-        <v>38.24</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H6">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -913,19 +691,19 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G7">
-        <v>15.79</v>
+        <v>89.47</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1027,7 +805,7 @@
         <v>28</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1073,7 +851,7 @@
         <v>34</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1096,7 +874,7 @@
         <v>19</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1207,19 +985,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>64.29000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1259,19 +1037,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="G6">
-        <v>38.24</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H6">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1285,19 +1063,19 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G7">
-        <v>15.79</v>
+        <v>89.47</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1307,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1345,10 +1123,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1368,10 +1146,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
         <v>40</v>
-      </c>
-      <c r="D3" t="s">
-        <v>84</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1391,10 +1169,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1414,10 +1192,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1437,10 +1215,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1454,22 +1232,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920280</v>
+        <v>20330051920279</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1477,22 +1255,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920206</v>
+        <v>20330051920141</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1500,734 +1278,47 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920209</v>
+        <v>20330051920136</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920213</v>
+        <v>20330051920317</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920177</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" t="s">
-        <v>92</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920217</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" t="s">
-        <v>93</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920279</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" t="s">
-        <v>94</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920115</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14" t="s">
-        <v>95</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920129</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" t="s">
-        <v>96</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920134</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" t="s">
-        <v>97</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920141</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" t="s">
-        <v>98</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920145</v>
-      </c>
-      <c r="B18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18" t="s">
-        <v>99</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920318</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" t="s">
-        <v>68</v>
-      </c>
-      <c r="D19" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920323</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" t="s">
-        <v>101</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920324</v>
-      </c>
-      <c r="B21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" t="s">
-        <v>40</v>
-      </c>
-      <c r="D21" t="s">
-        <v>102</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920325</v>
-      </c>
-      <c r="B22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" t="s">
-        <v>103</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920326</v>
-      </c>
-      <c r="B23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" t="s">
-        <v>71</v>
-      </c>
-      <c r="D23" t="s">
-        <v>104</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920327</v>
-      </c>
-      <c r="B24" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920330</v>
-      </c>
-      <c r="B25" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" t="s">
-        <v>72</v>
-      </c>
-      <c r="D25" t="s">
-        <v>106</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920333</v>
-      </c>
-      <c r="B26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26" t="s">
-        <v>61</v>
-      </c>
-      <c r="D26" t="s">
-        <v>107</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>15</v>
-      </c>
-      <c r="G26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920335</v>
-      </c>
-      <c r="B27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" t="s">
-        <v>73</v>
-      </c>
-      <c r="D27" t="s">
-        <v>108</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>20330051920197</v>
-      </c>
-      <c r="B28" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" t="s">
-        <v>74</v>
-      </c>
-      <c r="D28" t="s">
-        <v>109</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>12</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>20330051920116</v>
-      </c>
-      <c r="B29" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" t="s">
-        <v>75</v>
-      </c>
-      <c r="D29" t="s">
-        <v>110</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>20330051920128</v>
-      </c>
-      <c r="B30" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" t="s">
-        <v>76</v>
-      </c>
-      <c r="D30" t="s">
-        <v>111</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>14</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>20330051920131</v>
-      </c>
-      <c r="B31" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" t="s">
-        <v>77</v>
-      </c>
-      <c r="D31" t="s">
-        <v>112</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>20330051920136</v>
-      </c>
-      <c r="B32" t="s">
-        <v>48</v>
-      </c>
-      <c r="C32" t="s">
-        <v>71</v>
-      </c>
-      <c r="D32" t="s">
-        <v>113</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>20330051920140</v>
-      </c>
-      <c r="B33" t="s">
-        <v>49</v>
-      </c>
-      <c r="C33" t="s">
-        <v>78</v>
-      </c>
-      <c r="D33" t="s">
-        <v>114</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>14</v>
-      </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>20330051920142</v>
-      </c>
-      <c r="B34" t="s">
-        <v>50</v>
-      </c>
-      <c r="C34" t="s">
-        <v>30</v>
-      </c>
-      <c r="D34" t="s">
-        <v>115</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>14</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>20330051920143</v>
-      </c>
-      <c r="B35" t="s">
-        <v>51</v>
-      </c>
-      <c r="C35" t="s">
-        <v>79</v>
-      </c>
-      <c r="D35" t="s">
-        <v>116</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>14</v>
-      </c>
-      <c r="G35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>20330051920144</v>
-      </c>
-      <c r="B36" t="s">
-        <v>52</v>
-      </c>
-      <c r="C36" t="s">
-        <v>56</v>
-      </c>
-      <c r="D36" t="s">
-        <v>117</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>14</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>20330051920153</v>
-      </c>
-      <c r="B37" t="s">
-        <v>53</v>
-      </c>
-      <c r="D37" t="s">
-        <v>118</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>20330051920317</v>
-      </c>
-      <c r="B38" t="s">
-        <v>54</v>
-      </c>
-      <c r="C38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D38" t="s">
-        <v>119</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>15</v>
-      </c>
-      <c r="G38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>20330051920380</v>
-      </c>
-      <c r="B39" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39" t="s">
-        <v>81</v>
-      </c>
-      <c r="D39" t="s">
-        <v>120</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>15</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>20330051920331</v>
-      </c>
-      <c r="B40" t="s">
-        <v>30</v>
-      </c>
-      <c r="C40" t="s">
-        <v>82</v>
-      </c>
-      <c r="D40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s">
-        <v>15</v>
-      </c>
-      <c r="G40">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20212.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20212.xlsx
@@ -85,6 +85,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
     <t>ORTEGA</t>
   </si>
   <si>
@@ -106,12 +109,12 @@
     <t>OSORIO</t>
   </si>
   <si>
-    <t>MARCIAL</t>
-  </si>
-  <si>
     <t>APALE</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -130,12 +133,12 @@
     <t>MACHORRO</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
     <t>ALEXIS ISAI</t>
   </si>
   <si>
@@ -155,9 +158,6 @@
   </si>
   <si>
     <t>KARLA</t>
-  </si>
-  <si>
-    <t>IVAN DE JESUS</t>
   </si>
   <si>
     <t>JOSE MIGUEL</t>
@@ -587,19 +587,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>53.33</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -610,7 +610,7 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -619,13 +619,13 @@
         <v>2</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>92.86</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -665,16 +665,16 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>85.29000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H6">
         <v>8.6</v>
@@ -782,7 +782,7 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>34</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -959,19 +959,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>53.33</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -982,7 +982,7 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -991,13 +991,13 @@
         <v>2</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>92.86</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1037,16 +1037,16 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>85.29000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H6">
         <v>8.6</v>
@@ -1117,7 +1117,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920145</v>
+        <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -1140,22 +1140,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920087</v>
+        <v>21330051920145</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
         <v>40</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1163,7 +1163,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920091</v>
+        <v>20330051920087</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920065</v>
+        <v>20330051920091</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920068</v>
+        <v>20330051920065</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
@@ -1232,7 +1232,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920279</v>
+        <v>20330051920068</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
@@ -1247,7 +1247,7 @@
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1255,7 +1255,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920141</v>
+        <v>20330051920279</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
@@ -1270,7 +1270,7 @@
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1278,7 +1278,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920136</v>
+        <v>20330051920141</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
@@ -1296,7 +1296,7 @@
         <v>14</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">

--- a/docentes/González Nuñez Veronica - Estadisticos 20212.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20212.xlsx
@@ -94,21 +94,21 @@
     <t>MARROQUIN</t>
   </si>
   <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>OLMOS</t>
   </si>
   <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
     <t>APALE</t>
   </si>
   <si>
@@ -118,21 +118,21 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>URBINA</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
@@ -145,19 +145,19 @@
     <t>GABRIEL JOSUE</t>
   </si>
   <si>
+    <t>ALDIR ADALBERTO</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>MEILYN ADABEL</t>
+  </si>
+  <si>
     <t>ANGEL</t>
   </si>
   <si>
-    <t>ALDIR ADALBERTO</t>
-  </si>
-  <si>
     <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>AXEL YAEL</t>
-  </si>
-  <si>
-    <t>KARLA</t>
   </si>
   <si>
     <t>JOSE MIGUEL</t>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920091</v>
+        <v>20330051920065</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920065</v>
+        <v>20330051920141</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
@@ -1224,7 +1224,7 @@
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1232,7 +1232,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920068</v>
+        <v>20330051920148</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
@@ -1247,7 +1247,7 @@
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1255,7 +1255,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920279</v>
+        <v>20330051920091</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
@@ -1270,15 +1270,15 @@
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920141</v>
+        <v>20330051920068</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
@@ -1293,10 +1293,10 @@
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">

--- a/docentes/González Nuñez Veronica - Estadisticos 20212.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="36">
   <si>
     <t>Mat</t>
   </si>
@@ -97,18 +97,6 @@
     <t>SARMIENTO</t>
   </si>
   <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
     <t>APALE</t>
   </si>
   <si>
@@ -121,18 +109,6 @@
     <t>URBINA</t>
   </si>
   <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
@@ -146,18 +122,6 @@
   </si>
   <si>
     <t>ALDIR ADALBERTO</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>MEILYN ADABEL</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
   </si>
   <si>
     <t>JOSE MIGUEL</t>
@@ -587,19 +551,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>53.33</v>
+        <v>66.67</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -665,19 +629,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>88.23999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -756,16 +720,19 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>81.25</v>
+      </c>
+      <c r="H2">
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -779,16 +746,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>43.33</v>
+      </c>
+      <c r="H3">
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -802,16 +772,19 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>79.31</v>
+      </c>
+      <c r="H4">
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -825,16 +798,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>57.89</v>
+      </c>
+      <c r="H5">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -848,16 +824,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>79.41</v>
+      </c>
+      <c r="H6">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -871,16 +850,19 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>78.95</v>
+      </c>
+      <c r="H7">
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -959,19 +941,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>53.33</v>
+        <v>70</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -997,7 +979,7 @@
         <v>93.09999999999999</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1014,16 +996,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>63.16</v>
+        <v>68.42</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1037,19 +1019,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G6">
-        <v>88.23999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1066,16 +1048,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G7">
-        <v>89.47</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -1085,7 +1067,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1123,10 +1105,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
         <v>31</v>
-      </c>
-      <c r="D2" t="s">
-        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1146,10 +1128,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
         <v>32</v>
-      </c>
-      <c r="D3" t="s">
-        <v>40</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1169,10 +1151,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1192,10 +1174,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1209,116 +1191,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920141</v>
+        <v>20330051920317</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920148</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920091</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920068</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920317</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20212.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -85,43 +85,25 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
     <t>ORTEGA</t>
   </si>
   <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
+    <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>URBINA</t>
-  </si>
-  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
     <t>ALEXIS ISAI</t>
   </si>
   <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
-    <t>ALDIR ADALBERTO</t>
+    <t>JESUS URIEL</t>
   </si>
   <si>
     <t>JOSE MIGUEL</t>
@@ -525,10 +507,10 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>14</v>
@@ -537,7 +519,7 @@
         <v>87.5</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -551,19 +533,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>66.67</v>
+        <v>83.33</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -629,10 +611,10 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6">
         <v>31</v>
@@ -641,7 +623,7 @@
         <v>91.18000000000001</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -720,16 +702,16 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>81.25</v>
+        <v>87.5</v>
       </c>
       <c r="H2">
         <v>8.1</v>
@@ -746,19 +728,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>43.33</v>
+        <v>83.33</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -772,19 +754,19 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>79.31</v>
+        <v>89.66</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -798,19 +780,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>57.89</v>
+        <v>68.42</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -824,19 +806,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G6">
-        <v>79.41</v>
+        <v>94.12</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -850,19 +832,19 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G7">
-        <v>78.95</v>
+        <v>89.47</v>
       </c>
       <c r="H7">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -915,19 +897,19 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>87.5</v>
+        <v>93.75</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -941,19 +923,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>70</v>
+        <v>83.33</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -970,16 +952,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>93.09999999999999</v>
+        <v>89.66</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -996,16 +978,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G5">
-        <v>68.42</v>
+        <v>78.95</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1019,19 +1001,19 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G6">
-        <v>94.12</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1048,16 +1030,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G7">
-        <v>94.73999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="H7">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -1067,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1099,16 +1081,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920135</v>
+        <v>21330051920145</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
         <v>27</v>
-      </c>
-      <c r="D2" t="s">
-        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1122,22 +1104,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920145</v>
+        <v>20330051920259</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
         <v>28</v>
       </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1145,70 +1127,24 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920087</v>
+        <v>20330051920317</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920065</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920317</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20212.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20212.xlsx
@@ -85,12 +85,12 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>ORTEGA</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>APALE</t>
   </si>
   <si>
@@ -100,10 +100,10 @@
     <t>ESTEVEZ</t>
   </si>
   <si>
+    <t>JESUS URIEL</t>
+  </si>
+  <si>
     <t>ALEXIS ISAI</t>
-  </si>
-  <si>
-    <t>JESUS URIEL</t>
   </si>
   <si>
     <t>JOSE MIGUEL</t>
@@ -702,7 +702,7 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -714,7 +714,7 @@
         <v>87.5</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -935,7 +935,7 @@
         <v>83.33</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1081,22 +1081,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920145</v>
+        <v>20330051920259</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
         <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1104,25 +1104,25 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920259</v>
+        <v>21330051920145</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
